--- a/03_Outputs/Agua_Bosques_Turismo/09_Salud/salud.xlsx
+++ b/03_Outputs/Agua_Bosques_Turismo/09_Salud/salud.xlsx
@@ -1273,7 +1273,7 @@
         <v>2.14287821210148</v>
       </c>
       <c r="G14" s="11">
-        <v>80.7040732466597</v>
+        <v>80.7040732466598</v>
       </c>
     </row>
   </sheetData>
